--- a/data/trans_dic/P15B_tráfico-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15B_tráfico-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,0; 51,84</t>
+          <t>12,39; 49,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 33,19</t>
+          <t>10,73; 32,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 34,14</t>
+          <t>9,45; 33,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 18,14</t>
+          <t>3,9; 22,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 47,14</t>
+          <t>5,34; 44,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 23,41</t>
+          <t>4,12; 24,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 32,61</t>
+          <t>10,11; 32,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 29,36</t>
+          <t>9,34; 28,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 39,22</t>
+          <t>12,06; 38,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 24,57</t>
+          <t>9,4; 23,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 28,56</t>
+          <t>12,05; 28,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 19,32</t>
+          <t>8,04; 21,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,17; 52,92</t>
+          <t>21,68; 53,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,23; 33,96</t>
+          <t>14,57; 35,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 32,52</t>
+          <t>10,75; 33,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,72; 49,54</t>
+          <t>15,9; 45,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 41,55</t>
+          <t>8,41; 40,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 27,44</t>
+          <t>10,74; 28,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 31,35</t>
+          <t>8,35; 31,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,42; 45,13</t>
+          <t>14,76; 44,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,15; 42,68</t>
+          <t>20,29; 43,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,54; 28,13</t>
+          <t>14,67; 28,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 28,36</t>
+          <t>11,68; 27,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 40,78</t>
+          <t>19,34; 38,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 55,53</t>
+          <t>18,74; 55,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,07; 41,7</t>
+          <t>18,46; 42,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 35,27</t>
+          <t>8,42; 34,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 47,36</t>
+          <t>11,56; 45,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 44,02</t>
+          <t>7,97; 41,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,19; 36,86</t>
+          <t>14,24; 37,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 33,87</t>
+          <t>6,09; 32,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 28,21</t>
+          <t>4,38; 26,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 43,57</t>
+          <t>16,48; 43,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,57; 36,26</t>
+          <t>19,83; 35,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,61; 30,5</t>
+          <t>9,58; 28,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 29,41</t>
+          <t>9,14; 26,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,51; 44,34</t>
+          <t>13,58; 43,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 38,69</t>
+          <t>18,93; 37,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 37,45</t>
+          <t>15,66; 38,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24,48; 50,07</t>
+          <t>27,6; 52,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 44,3</t>
+          <t>7,89; 41,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,95; 32,66</t>
+          <t>12,35; 32,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 26,59</t>
+          <t>7,38; 27,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,65; 37,51</t>
+          <t>19,22; 37,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,67; 37,36</t>
+          <t>14,81; 39,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 32,83</t>
+          <t>17,99; 33,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 27,97</t>
+          <t>13,75; 28,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,34; 39,64</t>
+          <t>25,74; 41,44</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,44; 42,65</t>
+          <t>23,93; 41,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,63; 31,13</t>
+          <t>20,01; 31,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,73</t>
+          <t>15,98; 28,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,85; 35,57</t>
+          <t>20,99; 34,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,73; 29,85</t>
+          <t>13,58; 30,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,24</t>
+          <t>13,89; 24,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,19</t>
+          <t>12,07; 23,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,84; 28,19</t>
+          <t>16,69; 28,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,43; 33,86</t>
+          <t>22,05; 34,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,81; 26,05</t>
+          <t>19,02; 26,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,7</t>
+          <t>15,93; 23,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,76; 29,46</t>
+          <t>20,02; 29,06</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>12978</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2962; 11809</t>
+          <t>2822; 11353</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6492; 19592</t>
+          <t>6336; 18943</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3720; 13567</t>
+          <t>3756; 13479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>979; 8140</t>
+          <t>1936; 11078</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>849; 7479</t>
+          <t>848; 6988</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1951; 12283</t>
+          <t>2161; 12782</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4689; 15873</t>
+          <t>4923; 15594</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4251; 12697</t>
+          <t>4384; 13555</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4932; 15156</t>
+          <t>4663; 15055</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10750; 27394</t>
+          <t>10477; 26478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11154; 25252</t>
+          <t>10650; 25392</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6285; 17030</t>
+          <t>7767; 20385</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20589</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15306</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35895</t>
+          <t>38045</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9055; 22637</t>
+          <t>9276; 22955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12380; 27608</t>
+          <t>11846; 28959</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6168; 19668</t>
+          <t>6504; 20130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10399; 32760</t>
+          <t>11718; 33188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3085; 12520</t>
+          <t>2534; 12095</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7110; 20474</t>
+          <t>8012; 21261</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3987; 15237</t>
+          <t>4059; 15322</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8253; 25830</t>
+          <t>9267; 27750</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13964; 31119</t>
+          <t>14792; 31475</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22664; 43858</t>
+          <t>22873; 44033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13109; 30933</t>
+          <t>12740; 30276</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24535; 50305</t>
+          <t>26398; 52957</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13159</t>
+          <t>14100</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3679; 13218</t>
+          <t>4461; 13298</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10555; 24354</t>
+          <t>10784; 24690</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3046; 12931</t>
+          <t>3087; 12725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3344; 13845</t>
+          <t>3811; 14879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2040; 10614</t>
+          <t>1922; 10027</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8094; 21028</t>
+          <t>8126; 21165</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1991; 10691</t>
+          <t>1922; 10245</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1664; 12443</t>
+          <t>2167; 13114</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8023; 20879</t>
+          <t>7895; 20751</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22592; 41867</t>
+          <t>22899; 41486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7237; 20810</t>
+          <t>6533; 19682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7055; 21572</t>
+          <t>7540; 21999</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>45259</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4218; 14948</t>
+          <t>4578; 14774</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16089; 34147</t>
+          <t>16708; 33286</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9725; 22800</t>
+          <t>9535; 23547</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14414; 29485</t>
+          <t>17538; 33654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1911; 10494</t>
+          <t>1869; 9893</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8518; 23271</t>
+          <t>8802; 23414</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4322; 16651</t>
+          <t>4624; 17279</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13559; 25889</t>
+          <t>14027; 27011</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8418; 21446</t>
+          <t>8500; 22403</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28911; 52375</t>
+          <t>28693; 52938</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16753; 34546</t>
+          <t>16976; 35320</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31127; 50699</t>
+          <t>35138; 56578</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>100199</t>
+          <t>110382</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30076; 52497</t>
+          <t>29457; 50560</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59210; 89346</t>
+          <t>57422; 89055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31443; 54840</t>
+          <t>31603; 56501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39525; 70825</t>
+          <t>46168; 76711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12875; 28002</t>
+          <t>12735; 28731</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35916; 61910</t>
+          <t>35480; 61417</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23578; 44404</t>
+          <t>23115; 44219</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35970; 60207</t>
+          <t>38760; 66540</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46470; 73427</t>
+          <t>47830; 75745</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102019; 141291</t>
+          <t>103161; 144262</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60415; 92239</t>
+          <t>61994; 91738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>81571; 121571</t>
+          <t>90501; 131372</t>
         </is>
       </c>
     </row>
